--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>27/07 13:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>40</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>27/07 18:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>40</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>18</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>02/08 17:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>45</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>27/07 11:35</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>27/07 18:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>40</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>27/07 17:15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
+      <c r="F11" t="n">
+        <v>2.53</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>03/08 00:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F13" t="n">
+        <v>2.15</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>40</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>27/07 23:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F16" t="n">
+        <v>2.85</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>27/07 14:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
+      <c r="F18" t="n">
+        <v>2.72</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,52 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45865.08805001424</v>
+        <v>45865.08805001157</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Fortaleza </t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fortaleza FC – Alianza FC ValleduparPrimera A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>28/07 01:20</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>+1,26%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>45865.17198332679</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1279,10 +1279,8 @@
           <t>28/07 01:20</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>40</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1295,7 +1293,52 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45865.17198332679</v>
+        <v>45865.17198332176</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Golden Sta</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries – Connecticut SunUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>27/07 17:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>+1,45%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>45865.22790927746</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,10 +1322,8 @@
           <t>27/07 17:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>17</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1338,7 +1336,232 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45865.22790927746</v>
+        <v>45865.22790928241</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Union Magd</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Union Magdalena – Independiente MedellinPrimera A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>27/07 23:20</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>+53,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>45865.27364673401</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 3.5 - break1er participant | Leylah Fer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Leylah Fernandez – Anna KalinskayaWTA - Washington</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>27/07 18:30</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>55,5%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>+16,4%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>45865.27364673401</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Tembeta</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CA Tembetary Ypane – GuaraniPrimera Division</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>27/07 21:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>+4,37%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>45865.27364673401</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Indiana Fe</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Indiana Fever – Chicago SkyUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+1,20%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45865.27364673401</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Anderlecht</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Anderlecht – WesterloBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>27/07 11:30</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>36,3%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+0,91%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45865.27364673401</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,10 +1365,8 @@
           <t>27/07 23:20</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>60</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1381,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45865.27364673401</v>
+        <v>45865.27364673611</v>
       </c>
     </row>
     <row r="23">
@@ -1410,10 +1408,8 @@
           <t>27/07 18:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1426,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45865.27364673401</v>
+        <v>45865.27364673611</v>
       </c>
     </row>
     <row r="24">
@@ -1455,10 +1451,8 @@
           <t>27/07 21:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>40</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1471,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45865.27364673401</v>
+        <v>45865.27364673611</v>
       </c>
     </row>
     <row r="25">
@@ -1500,10 +1494,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>20</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1516,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45865.27364673401</v>
+        <v>45865.27364673611</v>
       </c>
     </row>
     <row r="26">
@@ -1545,10 +1537,8 @@
           <t>27/07 11:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
+      <c r="F26" t="n">
+        <v>2.78</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1561,7 +1551,322 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45865.27364673401</v>
+        <v>45865.27364673611</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 1 - aces | Alejandro </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Alejandro Davidovich-Fokina – Alex De MinaurATP - Washington</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>27/07 21:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>45,1%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+19,6%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45865.30672282579</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | 21-21er set | Rakhimova </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Rakhimova – Ka CrossWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21-21er set</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>28/07 00:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+7,61%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45865.30672282579</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 2.5 - tir cadré2e équipe | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Wisla PlockPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Moins que 2.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>27/07 12:45</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>46,4%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+3,44%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45865.30672282579</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | 21-22e set | D Collins </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>D Collins – V TomovaWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21-22e set</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>27/07 22:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>27,3%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+0,96%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45865.30672282579</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | 11-22e set | Osuigwe – </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Osuigwe – H BaptisteWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>11-22e set</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>27/07 23:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>27,3%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+0,96%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45865.30672282579</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Tie-break: Oui | Adam Walto</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Adam Walton – Benjamin BonziATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>27/07 15:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>41,0%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+0,49%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45865.30672282579</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Urawa Red </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Urawa Red Diamonds – Avispa FukuokaJ-League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>27/07 10:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+0,39%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45865.30672282579</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>27/07 21:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F27" t="n">
+        <v>2.65</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45865.30672282579</v>
+        <v>45865.30672282408</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>28/07 00:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="F28" t="n">
+        <v>4.33</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45865.30672282579</v>
+        <v>45865.30672282408</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>27/07 12:45</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.23</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45865.30672282579</v>
+        <v>45865.30672282408</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>27/07 22:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F30" t="n">
+        <v>3.7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45865.30672282579</v>
+        <v>45865.30672282408</v>
       </c>
     </row>
     <row r="31">
@@ -1760,10 +1752,8 @@
           <t>27/07 23:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F31" t="n">
+        <v>3.7</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1776,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45865.30672282579</v>
+        <v>45865.30672282408</v>
       </c>
     </row>
     <row r="32">
@@ -1805,10 +1795,8 @@
           <t>27/07 15:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F32" t="n">
+        <v>2.45</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1821,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45865.30672282579</v>
+        <v>45865.30672282408</v>
       </c>
     </row>
     <row r="33">
@@ -1850,10 +1838,8 @@
           <t>27/07 10:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>45</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1866,7 +1852,277 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45865.30672282579</v>
+        <v>45865.30672282408</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Atlanta Dr</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Atlanta Dream – Minnesota LynxUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>27/07 23:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+1,59%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45865.35293330025</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | 21-2 | Yafan Wang</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Yafan Wang – Yuliia StarodubtsevaWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>28/07 14:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>49,9%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+1,38%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45865.35293330025</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 3.5 - tir cadré2e équipe | Jagielloni</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystok – Widzew LodzPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Moins que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>27/07 15:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+1,05%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45865.35293330025</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Adam Walto</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Adam Walton – Benjamin BonziATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>27/07 15:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>50,5%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+0,99%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45865.35293330025</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | Moins que 9.52e participant | Vondrousov</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Vondrousova – Al EalaWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moins que 9.52e participant</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>27/07 16:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+0,18%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45865.35293330025</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | 11-21er set | E Ruse – E</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>E Ruse – E RaducanuWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>11-21er set</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>28/07 00:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>31,3%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+0,09%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45865.35293330025</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>27/07 23:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>25</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45865.35293330025</v>
+        <v>45865.35293329861</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>28/07 14:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
+      <c r="F35" t="n">
+        <v>2.03</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45865.35293330025</v>
+        <v>45865.35293329861</v>
       </c>
     </row>
     <row r="36">
@@ -1971,10 +1967,8 @@
           <t>27/07 15:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2.13</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1987,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45865.35293330025</v>
+        <v>45865.35293329861</v>
       </c>
     </row>
     <row r="37">
@@ -2016,10 +2010,8 @@
           <t>27/07 15:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2032,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45865.35293330025</v>
+        <v>45865.35293329861</v>
       </c>
     </row>
     <row r="38">
@@ -2061,10 +2053,8 @@
           <t>27/07 16:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2077,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45865.35293330025</v>
+        <v>45865.35293329861</v>
       </c>
     </row>
     <row r="39">
@@ -2106,10 +2096,8 @@
           <t>28/07 00:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F39" t="n">
+        <v>3.2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2122,7 +2110,97 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45865.35293330025</v>
+        <v>45865.35293329861</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Malmo FF –</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Malmo FF – Rigas Futbola SkolaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+20,5%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45865.39149224434</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 3.51er set2e participant | Jaqueline </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Jaqueline Adina Cristian – Marina StakusicWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 3.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>27/07 15:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+0,82%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45865.39149224434</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>60</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45865.39149224434</v>
+        <v>45865.39149224537</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>27/07 15:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.35</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,412 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45865.39149224434</v>
+        <v>45865.39149224537</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Internacio</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Internacional RS – Vasco de GamaBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>27/07 21:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>37,3%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45865.43331191364</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Wisla PlockPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>27/07 12:45</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+5,30%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45865.43331191364</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Jagielloni</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystok – Widzew LodzPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>27/07 15:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+3,75%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45865.43331191364</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 5.5 - tir cadré | Sao Paulo </t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP – FluminenseBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Moins que 5.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+3,67%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45865.43331191364</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | 11-21er set | Chirico – </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chirico – Je Bouzas ManeiroWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>11-21er set</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>27/07 16:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>32,3%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+3,29%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45865.43331191364</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FK Suduva </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FK Suduva – DziugasA Lyga</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>27/07 13:45</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+2,85%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45865.43331191364</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | CA Banfiel</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CA Banfield – Barracas CentralLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>28/07 23:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+2,82%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45865.43331191364</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | H 1 (+1.5)1er set | Pera – Ca </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Pera – Ca OsorioWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>H 1 (+1.5)1er set</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>27/07 18:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>51,0%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+1,98%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45865.43331191364</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | X2 | Angleterre</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Angleterre F. – Espagne F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>27/07 16:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+0,04%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45865.43331191364</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.95</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45865.43331191364</v>
+        <v>45865.43331190972</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>27/07 12:45</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45865.43331191364</v>
+        <v>45865.43331190972</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>27/07 15:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.65</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45865.43331191364</v>
+        <v>45865.43331190972</v>
       </c>
     </row>
     <row r="45">
@@ -2360,10 +2354,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F45" t="n">
+        <v>3.3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2376,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45865.43331191364</v>
+        <v>45865.43331190972</v>
       </c>
     </row>
     <row r="46">
@@ -2405,10 +2397,8 @@
           <t>27/07 16:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F46" t="n">
+        <v>3.2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2421,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45865.43331191364</v>
+        <v>45865.43331190972</v>
       </c>
     </row>
     <row r="47">
@@ -2450,10 +2440,8 @@
           <t>27/07 13:45</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>40</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2466,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45865.43331191364</v>
+        <v>45865.43331190972</v>
       </c>
     </row>
     <row r="48">
@@ -2495,10 +2483,8 @@
           <t>28/07 23:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>60</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2511,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45865.43331191364</v>
+        <v>45865.43331190972</v>
       </c>
     </row>
     <row r="49">
@@ -2540,10 +2526,8 @@
           <t>27/07 18:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2556,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45865.43331191364</v>
+        <v>45865.43331190972</v>
       </c>
     </row>
     <row r="50">
@@ -2585,10 +2569,8 @@
           <t>27/07 16:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
+      <c r="F50" t="n">
+        <v>1.23</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2601,7 +2583,277 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45865.43331191364</v>
+        <v>45865.43331190972</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | L.Zhu – V.</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>L.Zhu – V.GrachevaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>27/07 16:10</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+31,8%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45865.47173395421</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 3.5 - tir cadré2e équipe | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Wisla PlockPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>27/07 12:45</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>46,4%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+10,4%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45865.47173395421</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tir cadré | Internacio</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Internacional RS – Vasco de GamaBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>27/07 21:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>63,4%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+4,66%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45865.47173395421</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs1re équipe | Angleterre</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Angleterre F. – Espagne F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>27/07 16:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>56,6%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+3,04%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45865.47173395421</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | K.Birrell </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>K.Birrell – V.MbokoWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>27/07 17:20</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+1,76%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45865.47173395421</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 3.5 - tir cadré1re équipe | Korona Kie</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Korona Kielce – Legia VarsoviePologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>27/07 18:15</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>54,4%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+0,72%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45865.47173395421</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>27/07 16:10</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.75</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45865.47173395421</v>
+        <v>45865.47173395834</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>27/07 12:45</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.38</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45865.47173395421</v>
+        <v>45865.47173395834</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F53" t="n">
+        <v>1.65</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45865.47173395421</v>
+        <v>45865.47173395834</v>
       </c>
     </row>
     <row r="54">
@@ -2747,10 +2741,8 @@
           <t>27/07 16:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
+      <c r="F54" t="n">
+        <v>1.82</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2763,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45865.47173395421</v>
+        <v>45865.47173395834</v>
       </c>
     </row>
     <row r="55">
@@ -2792,10 +2784,8 @@
           <t>27/07 17:20</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="F55" t="n">
+        <v>5.5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2808,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45865.47173395421</v>
+        <v>45865.47173395834</v>
       </c>
     </row>
     <row r="56">
@@ -2837,10 +2827,8 @@
           <t>27/07 18:15</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F56" t="n">
+        <v>1.85</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2853,7 +2841,187 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45865.47173395421</v>
+        <v>45865.47173395834</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Huracan</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CA Huracan – Boca JuniorsLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>27/07 21:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+22,7%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45865.53160942631</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Deportivo </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra – Atletico TucumanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>28/07 19:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+7,19%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45865.53160942631</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 3.51er set2e participant | Suzan Lame</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Suzan Lamens – Polina KudermetovaWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moins que 3.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>27/07 15:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>34,0%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+5,42%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45865.53160942631</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sparta Prague – FK Mlada BoleslavSynot League</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>27/07 18:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+5,20%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45865.53160942631</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>50</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45865.53160942631</v>
+        <v>45865.5316094213</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>28/07 19:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>45</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45865.53160942631</v>
+        <v>45865.5316094213</v>
       </c>
     </row>
     <row r="59">
@@ -2960,10 +2956,8 @@
           <t>27/07 15:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F59" t="n">
+        <v>3.1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2976,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45865.53160942631</v>
+        <v>45865.5316094213</v>
       </c>
     </row>
     <row r="60">
@@ -3005,10 +2999,8 @@
           <t>27/07 18:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>45</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3021,7 +3013,97 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45865.53160942631</v>
+        <v>45865.5316094213</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 2.51er set2e participant | Jaqueline </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Jaqueline Adina Cristian – Marina StakusicWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Moins que 2.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>27/07 15:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+9,06%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45865.56455014055</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Club Bruge</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Club Bruges – GenkBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>27/07 16:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>62,9%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+0,02%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45865.56455014055</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>27/07 15:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F61" t="n">
+        <v>3.7</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45865.56455014055</v>
+        <v>45865.56455013889</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>27/07 16:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
+      <c r="F62" t="n">
+        <v>1.59</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,187 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45865.56455014055</v>
+        <v>45865.56455013889</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football | Plus que 14.5 - tirs2e équipe | Angleterre</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Angleterre F – Espagne FInternational - Euro (F) 2025</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>27/07 16:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>56,1%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+12,2%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45865.59747322095</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | Moins que 11.52e participant | Volynets –</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Volynets – Aoi ItoWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Moins que 11.52e participant</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>27/07 15:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+3,92%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45865.59747322095</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | H 1 (+2.5)1er set | Osuigwe – </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Osuigwe – H BaptisteWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>H 1 (+2.5)1er set</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>27/07 23:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>48,3%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+1,49%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45865.59747322095</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | FC Wintert</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FC Winterthur – Young Boys BerneSuisse. Suisse - Super League</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>02/08 16:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+0,55%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45865.59747322095</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>27/07 16:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45865.59747322095</v>
+        <v>45865.59747321759</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>27/07 15:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45865.59747322095</v>
+        <v>45865.59747321759</v>
       </c>
     </row>
     <row r="65">
@@ -3218,10 +3214,8 @@
           <t>27/07 23:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F65" t="n">
+        <v>2.1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3234,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45865.59747322095</v>
+        <v>45865.59747321759</v>
       </c>
     </row>
     <row r="66">
@@ -3263,10 +3257,8 @@
           <t>02/08 16:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>6</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3279,7 +3271,232 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45865.59747322095</v>
+        <v>45865.59747321759</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | H 2 (−3.5) | FC Spaeri </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FC Spaeri – Austria VienneEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>H 2 (−3.5)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>31/07 16:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>5.80</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>18,1%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+5,06%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45865.64100005171</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | Moins que 8.51er set | Bouchard –</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bouchard – Emil ArangoWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Moins que 8.51er set</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>28/07 00:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+3,43%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45865.64100005171</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Zeljeznica</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Zeljeznicar – FK Radnik BijeljinaPremijer Liga</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+3,07%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45865.64100005171</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Plus que 6.51er set2e participant | Sebastian </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Sebastian Ofner – Reilly OpelkaATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>27/07 16:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+2,51%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45865.64100005171</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | H 1 (+1.5)1er set | T Maria – </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>T Maria – SiegemundWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>H 1 (+1.5)1er set</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>28/07 00:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>48,6%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+2,06%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45865.64100005171</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>31/07 16:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>5.80</t>
-        </is>
+      <c r="F67" t="n">
+        <v>5.8</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45865.64100005171</v>
+        <v>45865.64100004629</v>
       </c>
     </row>
     <row r="68">
@@ -3345,10 +3343,8 @@
           <t>28/07 00:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F68" t="n">
+        <v>2.5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3361,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45865.64100005171</v>
+        <v>45865.64100004629</v>
       </c>
     </row>
     <row r="69">
@@ -3390,10 +3386,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>35</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3406,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45865.64100005171</v>
+        <v>45865.64100004629</v>
       </c>
     </row>
     <row r="70">
@@ -3435,10 +3429,8 @@
           <t>27/07 16:30</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F70" t="n">
+        <v>4.2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3451,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45865.64100005171</v>
+        <v>45865.64100004629</v>
       </c>
     </row>
     <row r="71">
@@ -3480,10 +3472,8 @@
           <t>28/07 00:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F71" t="n">
+        <v>2.1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3496,7 +3486,142 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45865.64100005171</v>
+        <v>45865.64100004629</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – PodbrezovaFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>02/08 18:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+2,59%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45865.68588201941</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Bahia Salv</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Bahia Salvador BA – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>27/07 21:30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+0,35%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45865.68588201941</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | Tie-break: Oui | Sebastian </t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Sebastian Ofner – Reilly OpelkaATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>27/07 16:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+0,22%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45865.68588201941</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>35</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45865.68588201941</v>
+        <v>45865.68588201389</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F73" t="n">
+        <v>2.55</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45865.68588201941</v>
+        <v>45865.68588201389</v>
       </c>
     </row>
     <row r="74">
@@ -3605,10 +3601,8 @@
           <t>27/07 16:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
+      <c r="F74" t="n">
+        <v>1.66</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3621,7 +3615,187 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45865.68588201941</v>
+        <v>45865.68588201389</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FK Panevez</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FK Panevezys – Banga GargzdaiA Lyga</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>28/07 16:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+17,0%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45865.72336619608</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−1.5) | Dan Martin</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Dan Martin – Jaume MunarATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>H 1 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>28/07 14:30</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+1,93%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45865.72336619608</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | H 2 (+1.5)1er set | Eva Lys – </t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Eva Lys – Leol JeanjeanWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>H 2 (+1.5)1er set</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>28/07 00:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>48,5%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+1,79%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45865.72336619608</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | H 2 (−2.5)1er set | Uchijima –</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Uchijima – M BouzkovaWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)1er set</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>28/07 00:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>47,7%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+0,19%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45865.72336619608</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3644,10 +3644,8 @@
           <t>28/07 16:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>40</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3660,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45865.72336619608</v>
+        <v>45865.72336619213</v>
       </c>
     </row>
     <row r="76">
@@ -3689,10 +3687,8 @@
           <t>28/07 14:30</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>50</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3705,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45865.72336619608</v>
+        <v>45865.72336619213</v>
       </c>
     </row>
     <row r="77">
@@ -3734,10 +3730,8 @@
           <t>28/07 00:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F77" t="n">
+        <v>2.1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3750,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45865.72336619608</v>
+        <v>45865.72336619213</v>
       </c>
     </row>
     <row r="78">
@@ -3779,10 +3773,8 @@
           <t>28/07 00:00</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F78" t="n">
+        <v>2.1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3795,7 +3787,187 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45865.72336619608</v>
+        <v>45865.72336619213</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Ruzomberok</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ruzomberok – MFK SkalicaFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>02/08 16:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+16,7%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45865.77202904277</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pas de buts | Bodø/Glimt</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bodø/Glimt – Strømsgodset IFNorvège - Norvège Eliteserien</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+5,75%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45865.77202904277</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Siauliai –</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Siauliai – Kauno ZalgirisA Lyga</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>28/07 16:00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+3,66%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45865.77202904277</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Phoenix Me</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury – Washington MysticsUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>27/07 22:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+0,60%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45865.77202904277</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3816,10 +3816,8 @@
           <t>02/08 16:00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>40</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3832,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45865.77202904277</v>
+        <v>45865.77202903936</v>
       </c>
     </row>
     <row r="80">
@@ -3861,10 +3859,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>50</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3877,7 +3873,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45865.77202904277</v>
+        <v>45865.77202903936</v>
       </c>
     </row>
     <row r="81">
@@ -3906,10 +3902,8 @@
           <t>28/07 16:00</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>35</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3922,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45865.77202904277</v>
+        <v>45865.77202903936</v>
       </c>
     </row>
     <row r="82">
@@ -3951,10 +3945,8 @@
           <t>27/07 22:00</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F82" t="n">
+        <v>25</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3967,7 +3959,142 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45865.77202904277</v>
+        <v>45865.77202903936</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Olimp</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Club Olimpia – CD RecoletaPrimera Division</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>30/07 21:15</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+44,7%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45865.80539769684</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | H 2 (−2.5)1er set | Bouchard –</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Bouchard – Emil ArangoWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)1er set</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>28/07 00:00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+0,86%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45865.80539769684</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Roman Safi</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Roman Safiullin – Ugo BlanchetATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>27/07 19:30</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>69,0%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+0,11%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45865.80539769684</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3988,10 +3988,8 @@
           <t>30/07 21:15</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F83" t="n">
+        <v>55</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4004,7 +4002,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45865.80539769684</v>
+        <v>45865.80539769676</v>
       </c>
     </row>
     <row r="84">
@@ -4033,10 +4031,8 @@
           <t>28/07 00:00</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F84" t="n">
+        <v>2.1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4049,7 +4045,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45865.80539769684</v>
+        <v>45865.80539769676</v>
       </c>
     </row>
     <row r="85">
@@ -4078,10 +4074,8 @@
           <t>27/07 19:30</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="F85" t="n">
+        <v>1.45</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4094,7 +4088,52 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45865.80539769684</v>
+        <v>45865.80539769676</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Internacio</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Internacional – Vasco da GamaSérie A</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>27/07 21:30</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+35,7%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45865.85113585604</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4117,10 +4117,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F86" t="n">
+        <v>60</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4133,7 +4131,52 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45865.85113585604</v>
+        <v>45865.85113585648</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Bahia Salv</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Bahia Salvador BA – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>27/07 21:30</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>+0,59%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45865.88984969008</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4160,10 +4160,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F87" t="n">
+        <v>3</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4176,7 +4174,52 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45865.88984969008</v>
+        <v>45865.8898496875</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football | 1X | Cfr Cluj –</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Cfr Cluj – FC LuganoCoupes d'Europe - Europa League</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>31/07 17:30</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>70,6%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>+0,99%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>45865.93209018857</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-27.xlsx
+++ b/data/valuebets_database_2025-07-27.xlsx
@@ -4203,10 +4203,8 @@
           <t>31/07 17:30</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
+      <c r="F88" t="n">
+        <v>1.43</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4219,7 +4217,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45865.93209018857</v>
+        <v>45865.93209018518</v>
       </c>
     </row>
   </sheetData>
